--- a/data/nzd0094/nzd0094.xlsx
+++ b/data/nzd0094/nzd0094.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD256"/>
+  <dimension ref="A1:AD257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24772,10 +24772,10 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>413.08</v>
+        <v>379.52</v>
       </c>
       <c r="C256" t="n">
-        <v>433.4</v>
+        <v>409.31</v>
       </c>
       <c r="D256" t="n">
         <v>390.26</v>
@@ -24858,6 +24858,102 @@
       <c r="AD256" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>381.58</v>
+      </c>
+      <c r="C257" t="n">
+        <v>411.3</v>
+      </c>
+      <c r="D257" t="n">
+        <v>395.88</v>
+      </c>
+      <c r="E257" t="n">
+        <v>377.62</v>
+      </c>
+      <c r="F257" t="n">
+        <v>370.42</v>
+      </c>
+      <c r="G257" t="n">
+        <v>363.83</v>
+      </c>
+      <c r="H257" t="n">
+        <v>360.1</v>
+      </c>
+      <c r="I257" t="n">
+        <v>359.94</v>
+      </c>
+      <c r="J257" t="n">
+        <v>360.76</v>
+      </c>
+      <c r="K257" t="n">
+        <v>364.25</v>
+      </c>
+      <c r="L257" t="n">
+        <v>367.1</v>
+      </c>
+      <c r="M257" t="n">
+        <v>375.09</v>
+      </c>
+      <c r="N257" t="n">
+        <v>378.94</v>
+      </c>
+      <c r="O257" t="n">
+        <v>373.13</v>
+      </c>
+      <c r="P257" t="n">
+        <v>371.24</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>371.35</v>
+      </c>
+      <c r="R257" t="n">
+        <v>370.81</v>
+      </c>
+      <c r="S257" t="n">
+        <v>378.07</v>
+      </c>
+      <c r="T257" t="n">
+        <v>382.57</v>
+      </c>
+      <c r="U257" t="n">
+        <v>389.58</v>
+      </c>
+      <c r="V257" t="n">
+        <v>390.72</v>
+      </c>
+      <c r="W257" t="n">
+        <v>390.31</v>
+      </c>
+      <c r="X257" t="n">
+        <v>391.71</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>384</v>
+      </c>
+      <c r="Z257" t="n">
+        <v>387.98</v>
+      </c>
+      <c r="AA257" t="n">
+        <v>373.77</v>
+      </c>
+      <c r="AB257" t="n">
+        <v>372.04</v>
+      </c>
+      <c r="AC257" t="n">
+        <v>376.77</v>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -24872,7 +24968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B259"/>
+  <dimension ref="A1:B260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27465,6 +27561,16 @@
       </c>
       <c r="B259" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -27633,28 +27739,28 @@
         <v>0.0102</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9710994336127883</v>
+        <v>0.9282859092483381</v>
       </c>
       <c r="J2" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K2" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03663034981847568</v>
+        <v>0.03385657115371399</v>
       </c>
       <c r="M2" t="n">
-        <v>26.51787833124594</v>
+        <v>26.42202000568925</v>
       </c>
       <c r="N2" t="n">
-        <v>1095.320620903897</v>
+        <v>1090.967959348736</v>
       </c>
       <c r="O2" t="n">
-        <v>33.09562842587971</v>
+        <v>33.0298041070294</v>
       </c>
       <c r="P2" t="n">
-        <v>369.0945375169459</v>
+        <v>369.6312628984664</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -27715,28 +27821,28 @@
         <v>0.0104</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9072043579004853</v>
+        <v>0.8893786164608097</v>
       </c>
       <c r="J3" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K3" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04898478607242152</v>
+        <v>0.04773262661999522</v>
       </c>
       <c r="M3" t="n">
-        <v>22.0744169279188</v>
+        <v>21.86766520778072</v>
       </c>
       <c r="N3" t="n">
-        <v>752.8085660363305</v>
+        <v>746.5974441243137</v>
       </c>
       <c r="O3" t="n">
-        <v>27.43735712557481</v>
+        <v>27.32393537037287</v>
       </c>
       <c r="P3" t="n">
-        <v>383.1605459515504</v>
+        <v>383.3780903428817</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -27797,28 +27903,28 @@
         <v>0.0106</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3562252170367</v>
+        <v>0.3607399078912868</v>
       </c>
       <c r="J4" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K4" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00841609304802815</v>
+        <v>0.008703615574289669</v>
       </c>
       <c r="M4" t="n">
-        <v>21.02585815779931</v>
+        <v>20.9645044651363</v>
       </c>
       <c r="N4" t="n">
-        <v>669.6342623625975</v>
+        <v>666.9238545930334</v>
       </c>
       <c r="O4" t="n">
-        <v>25.87729240787369</v>
+        <v>25.82486891724784</v>
       </c>
       <c r="P4" t="n">
-        <v>381.3555615406274</v>
+        <v>381.2994441773499</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -27879,28 +27985,28 @@
         <v>0.0239</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8222868297112325</v>
+        <v>0.8239298674393107</v>
       </c>
       <c r="J5" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K5" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08579404601740415</v>
+        <v>0.08678380417418108</v>
       </c>
       <c r="M5" t="n">
-        <v>15.05936947937661</v>
+        <v>15.00715362212292</v>
       </c>
       <c r="N5" t="n">
-        <v>339.874059482086</v>
+        <v>338.5401564069018</v>
       </c>
       <c r="O5" t="n">
-        <v>18.43567355650685</v>
+        <v>18.39946076402518</v>
       </c>
       <c r="P5" t="n">
-        <v>353.6689199425404</v>
+        <v>353.6492437997143</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27957,28 +28063,28 @@
         <v>0.0308</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3632786037954847</v>
+        <v>0.367968977960624</v>
       </c>
       <c r="J6" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K6" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02934552825852066</v>
+        <v>0.03032295701175503</v>
       </c>
       <c r="M6" t="n">
-        <v>11.70438965158031</v>
+        <v>11.67975212528392</v>
       </c>
       <c r="N6" t="n">
-        <v>201.0267560616739</v>
+        <v>200.3487203730613</v>
       </c>
       <c r="O6" t="n">
-        <v>14.17839046089766</v>
+        <v>14.1544593811654</v>
       </c>
       <c r="P6" t="n">
-        <v>355.236149639493</v>
+        <v>355.179339733784</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28035,28 +28141,28 @@
         <v>0.0359</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2822161743253921</v>
+        <v>0.2851539147030762</v>
       </c>
       <c r="J7" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K7" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02441460417680974</v>
+        <v>0.0251166923577848</v>
       </c>
       <c r="M7" t="n">
-        <v>10.22217208572892</v>
+        <v>10.19231899108197</v>
       </c>
       <c r="N7" t="n">
-        <v>147.7486380681802</v>
+        <v>147.2131611106396</v>
       </c>
       <c r="O7" t="n">
-        <v>12.15518975862492</v>
+        <v>12.13314308456962</v>
       </c>
       <c r="P7" t="n">
-        <v>352.8299836283933</v>
+        <v>352.7945851333516</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28113,28 +28219,28 @@
         <v>0.0369</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1928587518887722</v>
+        <v>0.1945218902133494</v>
       </c>
       <c r="J8" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K8" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01628966647287888</v>
+        <v>0.01670672215047608</v>
       </c>
       <c r="M8" t="n">
-        <v>8.292858736284995</v>
+        <v>8.266713303953319</v>
       </c>
       <c r="N8" t="n">
-        <v>104.274430759531</v>
+        <v>103.8787120641673</v>
       </c>
       <c r="O8" t="n">
-        <v>10.21148523768854</v>
+        <v>10.19209066208535</v>
       </c>
       <c r="P8" t="n">
-        <v>352.9825083877348</v>
+        <v>352.9624682935919</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28191,28 +28297,28 @@
         <v>0.0422</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2324308451460206</v>
+        <v>0.2333730218603604</v>
       </c>
       <c r="J9" t="n">
+        <v>256</v>
+      </c>
+      <c r="K9" t="n">
         <v>255</v>
       </c>
-      <c r="K9" t="n">
-        <v>254</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.03511972184740142</v>
+        <v>0.03568907710690694</v>
       </c>
       <c r="M9" t="n">
-        <v>6.733382150377911</v>
+        <v>6.710959409797243</v>
       </c>
       <c r="N9" t="n">
-        <v>69.45266911942335</v>
+        <v>69.18510924583842</v>
       </c>
       <c r="O9" t="n">
-        <v>8.333826799221553</v>
+        <v>8.317758667203469</v>
       </c>
       <c r="P9" t="n">
-        <v>352.6076990906341</v>
+        <v>352.5964045804287</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28269,28 +28375,28 @@
         <v>0.045</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2978079100161325</v>
+        <v>0.2970913892630845</v>
       </c>
       <c r="J10" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06115299220994819</v>
+        <v>0.06137004963840731</v>
       </c>
       <c r="M10" t="n">
-        <v>6.48369970215902</v>
+        <v>6.461462043288402</v>
       </c>
       <c r="N10" t="n">
-        <v>63.7960227114162</v>
+        <v>63.54764371800474</v>
       </c>
       <c r="O10" t="n">
-        <v>7.987241245349749</v>
+        <v>7.971677597469979</v>
       </c>
       <c r="P10" t="n">
-        <v>353.6381954424044</v>
+        <v>353.6467892375016</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28347,28 +28453,28 @@
         <v>0.0478</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3509657678589425</v>
+        <v>0.3500910878960899</v>
       </c>
       <c r="J11" t="n">
+        <v>256</v>
+      </c>
+      <c r="K11" t="n">
         <v>255</v>
       </c>
-      <c r="K11" t="n">
-        <v>254</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.0923786879520706</v>
+        <v>0.0926798555908408</v>
       </c>
       <c r="M11" t="n">
-        <v>6.150948653233783</v>
+        <v>6.13056024185048</v>
       </c>
       <c r="N11" t="n">
-        <v>56.6293359210511</v>
+        <v>56.41140003877445</v>
       </c>
       <c r="O11" t="n">
-        <v>7.525246568787703</v>
+        <v>7.510752295128261</v>
       </c>
       <c r="P11" t="n">
-        <v>355.886519674055</v>
+        <v>355.8970050549995</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28425,28 +28531,28 @@
         <v>0.0536</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2453930333382521</v>
+        <v>0.2426395431444107</v>
       </c>
       <c r="J12" t="n">
+        <v>256</v>
+      </c>
+      <c r="K12" t="n">
         <v>255</v>
       </c>
-      <c r="K12" t="n">
-        <v>254</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.06172418795834977</v>
+        <v>0.06086809604881083</v>
       </c>
       <c r="M12" t="n">
-        <v>5.170892345354253</v>
+        <v>5.163072708249704</v>
       </c>
       <c r="N12" t="n">
-        <v>42.83301542221779</v>
+        <v>42.7060691994839</v>
       </c>
       <c r="O12" t="n">
-        <v>6.544693684368871</v>
+        <v>6.534988079521178</v>
       </c>
       <c r="P12" t="n">
-        <v>363.7818676594266</v>
+        <v>363.814875610718</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28503,28 +28609,28 @@
         <v>0.0468</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2389754298749426</v>
+        <v>0.2360942994535022</v>
       </c>
       <c r="J13" t="n">
+        <v>256</v>
+      </c>
+      <c r="K13" t="n">
         <v>255</v>
       </c>
-      <c r="K13" t="n">
-        <v>254</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.06144125816413615</v>
+        <v>0.06048456131979318</v>
       </c>
       <c r="M13" t="n">
-        <v>5.259159745979696</v>
+        <v>5.250215220798575</v>
       </c>
       <c r="N13" t="n">
-        <v>40.82130812223858</v>
+        <v>40.70614272925919</v>
       </c>
       <c r="O13" t="n">
-        <v>6.38915550931722</v>
+        <v>6.380136576066314</v>
       </c>
       <c r="P13" t="n">
-        <v>372.1020183036763</v>
+        <v>372.1365563647989</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28581,28 +28687,28 @@
         <v>0.0508</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1219863130477474</v>
+        <v>0.1164422279339888</v>
       </c>
       <c r="J14" t="n">
+        <v>256</v>
+      </c>
+      <c r="K14" t="n">
         <v>255</v>
       </c>
-      <c r="K14" t="n">
-        <v>254</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.02087513691747656</v>
+        <v>0.01912260186669323</v>
       </c>
       <c r="M14" t="n">
-        <v>4.678693305727914</v>
+        <v>4.683638339658531</v>
       </c>
       <c r="N14" t="n">
-        <v>32.6595361663283</v>
+        <v>32.69778395935361</v>
       </c>
       <c r="O14" t="n">
-        <v>5.714852243612979</v>
+        <v>5.718197614576958</v>
       </c>
       <c r="P14" t="n">
-        <v>382.2336063501829</v>
+        <v>382.3000670522403</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28659,28 +28765,28 @@
         <v>0.0555</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1125957886593762</v>
+        <v>0.1068358226940875</v>
       </c>
       <c r="J15" t="n">
+        <v>256</v>
+      </c>
+      <c r="K15" t="n">
         <v>255</v>
       </c>
-      <c r="K15" t="n">
-        <v>254</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.01747379152966</v>
+        <v>0.01580986511641502</v>
       </c>
       <c r="M15" t="n">
-        <v>4.698513942253919</v>
+        <v>4.704701001095144</v>
       </c>
       <c r="N15" t="n">
-        <v>33.35648993361901</v>
+        <v>33.4052097579566</v>
       </c>
       <c r="O15" t="n">
-        <v>5.77550776413806</v>
+        <v>5.779724020916276</v>
       </c>
       <c r="P15" t="n">
-        <v>376.9226361112959</v>
+        <v>376.9916847232896</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28737,28 +28843,28 @@
         <v>0.0487</v>
       </c>
       <c r="I16" t="n">
-        <v>0.001018041200342451</v>
+        <v>-0.004352270014709162</v>
       </c>
       <c r="J16" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K16" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L16" t="n">
-        <v>1.160489805029918e-06</v>
+        <v>2.131333512545019e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>5.336922255967849</v>
+        <v>5.336845186980011</v>
       </c>
       <c r="N16" t="n">
-        <v>41.83723533937064</v>
+        <v>41.82850823864623</v>
       </c>
       <c r="O16" t="n">
-        <v>6.468170942343024</v>
+        <v>6.467496288259177</v>
       </c>
       <c r="P16" t="n">
-        <v>377.5501802194036</v>
+        <v>377.6146686253992</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28815,28 +28921,28 @@
         <v>0.0534</v>
       </c>
       <c r="I17" t="n">
-        <v>0.03433895102589848</v>
+        <v>0.03017726722683511</v>
       </c>
       <c r="J17" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K17" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L17" t="n">
-        <v>0.001252416106922283</v>
+        <v>0.0009738066384197275</v>
       </c>
       <c r="M17" t="n">
-        <v>5.210191430516201</v>
+        <v>5.206764039016842</v>
       </c>
       <c r="N17" t="n">
-        <v>44.05094700727015</v>
+        <v>43.97089907364378</v>
       </c>
       <c r="O17" t="n">
-        <v>6.637088744869255</v>
+        <v>6.631055653034725</v>
       </c>
       <c r="P17" t="n">
-        <v>375.3376169477885</v>
+        <v>375.387591771167</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28893,28 +28999,28 @@
         <v>0.0579</v>
       </c>
       <c r="I18" t="n">
-        <v>0.04688562913816065</v>
+        <v>0.04139712508212973</v>
       </c>
       <c r="J18" t="n">
+        <v>256</v>
+      </c>
+      <c r="K18" t="n">
         <v>255</v>
       </c>
-      <c r="K18" t="n">
-        <v>254</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.00262301400971765</v>
+        <v>0.00205519163816581</v>
       </c>
       <c r="M18" t="n">
-        <v>5.144017609995703</v>
+        <v>5.14373594251397</v>
       </c>
       <c r="N18" t="n">
-        <v>39.11265385578751</v>
+        <v>39.1222771210065</v>
       </c>
       <c r="O18" t="n">
-        <v>6.254011021399588</v>
+        <v>6.254780341547295</v>
       </c>
       <c r="P18" t="n">
-        <v>376.0417416587713</v>
+        <v>376.1075360730568</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28971,28 +29077,28 @@
         <v>0.053</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1004720331758395</v>
+        <v>0.09694195162897445</v>
       </c>
       <c r="J19" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K19" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0108469240344129</v>
+        <v>0.01017647953785616</v>
       </c>
       <c r="M19" t="n">
-        <v>5.361309088893889</v>
+        <v>5.355412982077236</v>
       </c>
       <c r="N19" t="n">
-        <v>43.41155664698206</v>
+        <v>43.31011419898169</v>
       </c>
       <c r="O19" t="n">
-        <v>6.588744694323954</v>
+        <v>6.581042029875033</v>
       </c>
       <c r="P19" t="n">
-        <v>379.58851312774</v>
+        <v>379.6306140880366</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -29049,28 +29155,28 @@
         <v>0.049</v>
       </c>
       <c r="I20" t="n">
-        <v>0.07091350398038489</v>
+        <v>0.06736730269619014</v>
       </c>
       <c r="J20" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K20" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L20" t="n">
-        <v>0.00551197957323335</v>
+        <v>0.005012433376680225</v>
       </c>
       <c r="M20" t="n">
-        <v>5.092928793897526</v>
+        <v>5.087368525830215</v>
       </c>
       <c r="N20" t="n">
-        <v>41.78316599893578</v>
+        <v>41.68463039258245</v>
       </c>
       <c r="O20" t="n">
-        <v>6.46398994421679</v>
+        <v>6.45636355796221</v>
       </c>
       <c r="P20" t="n">
-        <v>384.7996182797995</v>
+        <v>384.8425699406878</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -29127,28 +29233,28 @@
         <v>0.0506</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2009113996227978</v>
+        <v>0.1974456354903442</v>
       </c>
       <c r="J21" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K21" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L21" t="n">
-        <v>0.04401569770229485</v>
+        <v>0.04286420250382417</v>
       </c>
       <c r="M21" t="n">
-        <v>4.903056836534188</v>
+        <v>4.897118634613824</v>
       </c>
       <c r="N21" t="n">
-        <v>40.70018766511808</v>
+        <v>40.60426577348932</v>
       </c>
       <c r="O21" t="n">
-        <v>6.3796698711703</v>
+        <v>6.372147657853616</v>
       </c>
       <c r="P21" t="n">
-        <v>388.2699264234839</v>
+        <v>388.3116873753332</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -29205,28 +29311,28 @@
         <v>0.057</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1580577396315468</v>
+        <v>0.157381889805849</v>
       </c>
       <c r="J22" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K22" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L22" t="n">
-        <v>0.03481300472355753</v>
+        <v>0.03481238295686684</v>
       </c>
       <c r="M22" t="n">
-        <v>4.38701254079697</v>
+        <v>4.372521528601094</v>
       </c>
       <c r="N22" t="n">
-        <v>32.66326214707538</v>
+        <v>32.53816871591853</v>
       </c>
       <c r="O22" t="n">
-        <v>5.715178225311559</v>
+        <v>5.704223761031691</v>
       </c>
       <c r="P22" t="n">
-        <v>387.291311118562</v>
+        <v>387.2993715348159</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -29283,28 +29389,28 @@
         <v>0.0611</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1954960335723704</v>
+        <v>0.1953201342640119</v>
       </c>
       <c r="J23" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K23" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L23" t="n">
-        <v>0.05131100230860497</v>
+        <v>0.05164415706668735</v>
       </c>
       <c r="M23" t="n">
-        <v>4.40279048245338</v>
+        <v>4.386306275720955</v>
       </c>
       <c r="N23" t="n">
-        <v>33.3232488692949</v>
+        <v>33.19324909799992</v>
       </c>
       <c r="O23" t="n">
-        <v>5.772629285628422</v>
+        <v>5.761358268498838</v>
       </c>
       <c r="P23" t="n">
-        <v>385.2883459172842</v>
+        <v>385.2904437526173</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -29361,28 +29467,28 @@
         <v>0.064</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2575916123081337</v>
+        <v>0.2585251310813488</v>
       </c>
       <c r="J24" t="n">
+        <v>256</v>
+      </c>
+      <c r="K24" t="n">
         <v>255</v>
       </c>
-      <c r="K24" t="n">
-        <v>254</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.07273698699486653</v>
+        <v>0.07380497911555306</v>
       </c>
       <c r="M24" t="n">
-        <v>4.991723270101566</v>
+        <v>4.976141260966777</v>
       </c>
       <c r="N24" t="n">
-        <v>39.94474008275032</v>
+        <v>39.79287333871022</v>
       </c>
       <c r="O24" t="n">
-        <v>6.320185130417488</v>
+        <v>6.308159267069136</v>
       </c>
       <c r="P24" t="n">
-        <v>383.7074566460648</v>
+        <v>383.696317877742</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -29439,28 +29545,28 @@
         <v>0.0766</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2024875751316525</v>
+        <v>0.2033095031169549</v>
       </c>
       <c r="J25" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K25" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L25" t="n">
-        <v>0.06634964699091217</v>
+        <v>0.06738503592008327</v>
       </c>
       <c r="M25" t="n">
-        <v>4.141299706749907</v>
+        <v>4.128858681888544</v>
       </c>
       <c r="N25" t="n">
-        <v>27.20824179262455</v>
+        <v>27.10565329792385</v>
       </c>
       <c r="O25" t="n">
-        <v>5.216152010114788</v>
+        <v>5.206308989862573</v>
       </c>
       <c r="P25" t="n">
-        <v>377.601843197405</v>
+        <v>377.592040603041</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -29517,28 +29623,28 @@
         <v>0.0496</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1482256284468029</v>
+        <v>0.1490538743008962</v>
       </c>
       <c r="J26" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K26" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L26" t="n">
-        <v>0.02735093558988577</v>
+        <v>0.02787912633627021</v>
       </c>
       <c r="M26" t="n">
-        <v>4.59139987939898</v>
+        <v>4.57741281900541</v>
       </c>
       <c r="N26" t="n">
-        <v>36.84585658650093</v>
+        <v>36.70567816157173</v>
       </c>
       <c r="O26" t="n">
-        <v>6.070078795740705</v>
+        <v>6.058521120007071</v>
       </c>
       <c r="P26" t="n">
-        <v>383.0252264548109</v>
+        <v>383.0153485113822</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -29595,28 +29701,28 @@
         <v>0.0752</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1894514388402857</v>
+        <v>0.1909361070269497</v>
       </c>
       <c r="J27" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K27" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L27" t="n">
-        <v>0.062082245291183</v>
+        <v>0.06348068298651233</v>
       </c>
       <c r="M27" t="n">
-        <v>3.872757244196167</v>
+        <v>3.86505012686645</v>
       </c>
       <c r="N27" t="n">
-        <v>25.57120699426272</v>
+        <v>25.48337129330296</v>
       </c>
       <c r="O27" t="n">
-        <v>5.056798097043496</v>
+        <v>5.048105713364465</v>
       </c>
       <c r="P27" t="n">
-        <v>366.9331744503289</v>
+        <v>366.915467789576</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -29673,28 +29779,28 @@
         <v>0.0784</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1778713240656229</v>
+        <v>0.1811689281465899</v>
       </c>
       <c r="J28" t="n">
+        <v>256</v>
+      </c>
+      <c r="K28" t="n">
         <v>255</v>
       </c>
-      <c r="K28" t="n">
-        <v>254</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.04114250257147456</v>
+        <v>0.04289913740717266</v>
       </c>
       <c r="M28" t="n">
-        <v>4.592047200847765</v>
+        <v>4.587960182896007</v>
       </c>
       <c r="N28" t="n">
-        <v>34.72482008530839</v>
+        <v>34.64806780079201</v>
       </c>
       <c r="O28" t="n">
-        <v>5.892776941757458</v>
+        <v>5.886260935499887</v>
       </c>
       <c r="P28" t="n">
-        <v>363.36633075741</v>
+        <v>363.3269250111661</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -29751,28 +29857,28 @@
         <v>0.1741</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0257293924431605</v>
+        <v>0.02939015657388858</v>
       </c>
       <c r="J29" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K29" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L29" t="n">
-        <v>0.001181933820489145</v>
+        <v>0.001550610635224214</v>
       </c>
       <c r="M29" t="n">
-        <v>3.907138561917464</v>
+        <v>3.906196246777758</v>
       </c>
       <c r="N29" t="n">
-        <v>26.4159865134633</v>
+        <v>26.38554095744536</v>
       </c>
       <c r="O29" t="n">
-        <v>5.139648481507592</v>
+        <v>5.136685795086688</v>
       </c>
       <c r="P29" t="n">
-        <v>371.728917641992</v>
+        <v>371.6851860168828</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -29810,7 +29916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD256"/>
+  <dimension ref="A1:AD257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68177,12 +68283,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>-35.6321314138674,174.51546221824614</t>
+          <t>-35.631997433601036,174.51512997968186</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>-35.632863690549065,174.51525702453299</t>
+          <t>-35.63276751700811,174.51501853518468</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -68318,6 +68424,158 @@
       <c r="AD256" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>-35.632005657685184,174.515150373317</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>-35.632775461623794,174.5150382360271</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>-35.63336504908454,174.51447921779948</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>-35.63395655932966,174.5138844193694</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>-35.63449211660001,174.5132478550879</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>-35.63498169925502,174.51257205791686</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>-35.63548650549674,174.51192126840292</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>-35.63601332644827,174.51129916037598</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>-35.63654998793015,174.510689976852</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>-35.637104093664114,174.51010424676957</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>-35.637654293312416,174.50951333374903</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>-35.638233609180276,174.50896624958676</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>-35.63879343747448,174.50843189222826</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>-35.63939764034943,174.50795729019652</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>-35.640032241261984,174.50751231916473</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>-35.640676230786426,174.50708641822706</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>-35.64130853794685,174.5066330743747</t>
+        </is>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>-35.64196719189927,174.5062365469086</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>-35.64261237933604,174.50581419376087</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>-35.64325995166985,174.50542141868837</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>-35.643905757555004,174.50504058714935</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>-35.644562784711056,174.5046572654033</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>-35.64521621963907,174.5042968830577</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>-35.64586963046411,174.50392972659188</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>-35.64657257862751,174.50369059524922</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>-35.64722696153237,174.50325964415103</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>-35.64791038318497,174.5029611985492</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>-35.648625093064005,174.5028371947794</t>
+        </is>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0094/nzd0094.xlsx
+++ b/data/nzd0094/nzd0094.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD257"/>
+  <dimension ref="A1:AD259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24957,6 +24957,198 @@
         </is>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>380.97</v>
+      </c>
+      <c r="C258" t="n">
+        <v>411.82</v>
+      </c>
+      <c r="D258" t="n">
+        <v>388.61</v>
+      </c>
+      <c r="E258" t="n">
+        <v>376.82</v>
+      </c>
+      <c r="F258" t="n">
+        <v>368.66</v>
+      </c>
+      <c r="G258" t="n">
+        <v>361.58</v>
+      </c>
+      <c r="H258" t="n">
+        <v>357.38</v>
+      </c>
+      <c r="I258" t="n">
+        <v>357.75</v>
+      </c>
+      <c r="J258" t="n">
+        <v>359.66</v>
+      </c>
+      <c r="K258" t="n">
+        <v>363.13</v>
+      </c>
+      <c r="L258" t="n">
+        <v>366.07</v>
+      </c>
+      <c r="M258" t="n">
+        <v>374</v>
+      </c>
+      <c r="N258" t="n">
+        <v>377.96</v>
+      </c>
+      <c r="O258" t="n">
+        <v>372.55</v>
+      </c>
+      <c r="P258" t="n">
+        <v>369.82</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>370.48</v>
+      </c>
+      <c r="R258" t="n">
+        <v>369.46</v>
+      </c>
+      <c r="S258" t="n">
+        <v>377.83</v>
+      </c>
+      <c r="T258" t="n">
+        <v>381.19</v>
+      </c>
+      <c r="U258" t="n">
+        <v>389.42</v>
+      </c>
+      <c r="V258" t="n">
+        <v>389.59</v>
+      </c>
+      <c r="W258" t="n">
+        <v>389.84</v>
+      </c>
+      <c r="X258" t="n">
+        <v>390.77</v>
+      </c>
+      <c r="Y258" t="n">
+        <v>383.52</v>
+      </c>
+      <c r="Z258" t="n">
+        <v>386.79</v>
+      </c>
+      <c r="AA258" t="n">
+        <v>373.07</v>
+      </c>
+      <c r="AB258" t="n">
+        <v>370.97</v>
+      </c>
+      <c r="AC258" t="n">
+        <v>376.95</v>
+      </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>380.55</v>
+      </c>
+      <c r="C259" t="n">
+        <v>411.84</v>
+      </c>
+      <c r="D259" t="n">
+        <v>393.29</v>
+      </c>
+      <c r="E259" t="n">
+        <v>376.81</v>
+      </c>
+      <c r="F259" t="n">
+        <v>368.75</v>
+      </c>
+      <c r="G259" t="n">
+        <v>362.34</v>
+      </c>
+      <c r="H259" t="n">
+        <v>357.3</v>
+      </c>
+      <c r="I259" t="n">
+        <v>357.86</v>
+      </c>
+      <c r="J259" t="n">
+        <v>359.73</v>
+      </c>
+      <c r="K259" t="n">
+        <v>363.11</v>
+      </c>
+      <c r="L259" t="n">
+        <v>366.69</v>
+      </c>
+      <c r="M259" t="n">
+        <v>374.08</v>
+      </c>
+      <c r="N259" t="n">
+        <v>378.5</v>
+      </c>
+      <c r="O259" t="n">
+        <v>372.14</v>
+      </c>
+      <c r="P259" t="n">
+        <v>370.15</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>370.48</v>
+      </c>
+      <c r="R259" t="n">
+        <v>370.66</v>
+      </c>
+      <c r="S259" t="n">
+        <v>377.62</v>
+      </c>
+      <c r="T259" t="n">
+        <v>382</v>
+      </c>
+      <c r="U259" t="n">
+        <v>389.75</v>
+      </c>
+      <c r="V259" t="n">
+        <v>390.02</v>
+      </c>
+      <c r="W259" t="n">
+        <v>389.95</v>
+      </c>
+      <c r="X259" t="n">
+        <v>391.17</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>383.72</v>
+      </c>
+      <c r="Z259" t="n">
+        <v>387.68</v>
+      </c>
+      <c r="AA259" t="n">
+        <v>373.5</v>
+      </c>
+      <c r="AB259" t="n">
+        <v>372.66</v>
+      </c>
+      <c r="AC259" t="n">
+        <v>376.85</v>
+      </c>
+      <c r="AD259" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24968,7 +25160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B260"/>
+  <dimension ref="A1:B262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27571,6 +27763,26 @@
       </c>
       <c r="B260" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -27739,28 +27951,28 @@
         <v>0.0102</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9282859092483381</v>
+        <v>0.9035317750002421</v>
       </c>
       <c r="J2" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K2" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03385657115371399</v>
+        <v>0.03263468359010058</v>
       </c>
       <c r="M2" t="n">
-        <v>26.42202000568925</v>
+        <v>26.29625004604875</v>
       </c>
       <c r="N2" t="n">
-        <v>1090.967959348736</v>
+        <v>1083.356797584514</v>
       </c>
       <c r="O2" t="n">
-        <v>33.0298041070294</v>
+        <v>32.91438587585243</v>
       </c>
       <c r="P2" t="n">
-        <v>369.6312628984664</v>
+        <v>369.9430680425734</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -27821,28 +28033,28 @@
         <v>0.0104</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8893786164608097</v>
+        <v>0.8973721608038394</v>
       </c>
       <c r="J3" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K3" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04773262661999522</v>
+        <v>0.04933317564817508</v>
       </c>
       <c r="M3" t="n">
-        <v>21.86766520778072</v>
+        <v>21.72566601057404</v>
       </c>
       <c r="N3" t="n">
-        <v>746.5974441243137</v>
+        <v>740.2829872461078</v>
       </c>
       <c r="O3" t="n">
-        <v>27.32393537037287</v>
+        <v>27.2081419293216</v>
       </c>
       <c r="P3" t="n">
-        <v>383.3780903428817</v>
+        <v>383.2798996419119</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -27903,28 +28115,28 @@
         <v>0.0106</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3607399078912868</v>
+        <v>0.3606883653838632</v>
       </c>
       <c r="J4" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K4" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008703615574289669</v>
+        <v>0.00885299222349567</v>
       </c>
       <c r="M4" t="n">
-        <v>20.9645044651363</v>
+        <v>20.80922394905328</v>
       </c>
       <c r="N4" t="n">
-        <v>666.9238545930334</v>
+        <v>661.4117666346567</v>
       </c>
       <c r="O4" t="n">
-        <v>25.82486891724784</v>
+        <v>25.71792695056615</v>
       </c>
       <c r="P4" t="n">
-        <v>381.2994441773499</v>
+        <v>381.3000646898298</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -27985,28 +28197,28 @@
         <v>0.0239</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8239298674393107</v>
+        <v>0.8256743349068584</v>
       </c>
       <c r="J5" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K5" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08678380417418108</v>
+        <v>0.08848283745521768</v>
       </c>
       <c r="M5" t="n">
-        <v>15.00715362212292</v>
+        <v>14.89686823595663</v>
       </c>
       <c r="N5" t="n">
-        <v>338.5401564069018</v>
+        <v>335.8829533583887</v>
       </c>
       <c r="O5" t="n">
-        <v>18.39946076402518</v>
+        <v>18.32710979282846</v>
       </c>
       <c r="P5" t="n">
-        <v>353.6492437997143</v>
+        <v>353.628291394464</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28063,28 +28275,28 @@
         <v>0.0308</v>
       </c>
       <c r="I6" t="n">
-        <v>0.367968977960624</v>
+        <v>0.3741257605766752</v>
       </c>
       <c r="J6" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K6" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03032295701175503</v>
+        <v>0.03182514780980494</v>
       </c>
       <c r="M6" t="n">
-        <v>11.67975212528392</v>
+        <v>11.61608501780749</v>
       </c>
       <c r="N6" t="n">
-        <v>200.3487203730613</v>
+        <v>198.8792537056043</v>
       </c>
       <c r="O6" t="n">
-        <v>14.1544593811654</v>
+        <v>14.10245559133601</v>
       </c>
       <c r="P6" t="n">
-        <v>355.179339733784</v>
+        <v>355.104553627757</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28141,28 +28353,28 @@
         <v>0.0359</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2851539147030762</v>
+        <v>0.2876798095174832</v>
       </c>
       <c r="J7" t="n">
+        <v>258</v>
+      </c>
+      <c r="K7" t="n">
         <v>256</v>
       </c>
-      <c r="K7" t="n">
-        <v>254</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0251166923577848</v>
+        <v>0.02598033111056319</v>
       </c>
       <c r="M7" t="n">
-        <v>10.19231899108197</v>
+        <v>10.12157755442545</v>
       </c>
       <c r="N7" t="n">
-        <v>147.2131611106396</v>
+        <v>146.0814861976805</v>
       </c>
       <c r="O7" t="n">
-        <v>12.13314308456962</v>
+        <v>12.08641742608952</v>
       </c>
       <c r="P7" t="n">
-        <v>352.7945851333516</v>
+        <v>352.7640580568375</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28219,28 +28431,28 @@
         <v>0.0369</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1945218902133494</v>
+        <v>0.1931126630028509</v>
       </c>
       <c r="J8" t="n">
+        <v>258</v>
+      </c>
+      <c r="K8" t="n">
         <v>256</v>
       </c>
-      <c r="K8" t="n">
-        <v>254</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.01670672215047608</v>
+        <v>0.01674927645631052</v>
       </c>
       <c r="M8" t="n">
-        <v>8.266713303953319</v>
+        <v>8.209532810082091</v>
       </c>
       <c r="N8" t="n">
-        <v>103.8787120641673</v>
+        <v>103.0725683143961</v>
       </c>
       <c r="O8" t="n">
-        <v>10.19209066208535</v>
+        <v>10.15246611983493</v>
       </c>
       <c r="P8" t="n">
-        <v>352.9624682935919</v>
+        <v>352.9794982985472</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28297,28 +28509,28 @@
         <v>0.0422</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2333730218603604</v>
+        <v>0.2316199649906431</v>
       </c>
       <c r="J9" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K9" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03568907710690694</v>
+        <v>0.03575565816560022</v>
       </c>
       <c r="M9" t="n">
-        <v>6.710959409797243</v>
+        <v>6.667449551458214</v>
       </c>
       <c r="N9" t="n">
-        <v>69.18510924583842</v>
+        <v>68.65516367792218</v>
       </c>
       <c r="O9" t="n">
-        <v>8.317758667203469</v>
+        <v>8.285841156932841</v>
       </c>
       <c r="P9" t="n">
-        <v>352.5964045804287</v>
+        <v>352.617480185073</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28375,28 +28587,28 @@
         <v>0.045</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2970913892630845</v>
+        <v>0.2938860118853702</v>
       </c>
       <c r="J10" t="n">
+        <v>258</v>
+      </c>
+      <c r="K10" t="n">
         <v>256</v>
       </c>
-      <c r="K10" t="n">
-        <v>254</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.06137004963840731</v>
+        <v>0.06108053741700548</v>
       </c>
       <c r="M10" t="n">
-        <v>6.461462043288402</v>
+        <v>6.425476020723381</v>
       </c>
       <c r="N10" t="n">
-        <v>63.54764371800474</v>
+        <v>63.07947877898627</v>
       </c>
       <c r="O10" t="n">
-        <v>7.971677597469979</v>
+        <v>7.942259047587548</v>
       </c>
       <c r="P10" t="n">
-        <v>353.6467892375016</v>
+        <v>353.6853456687534</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28453,28 +28665,28 @@
         <v>0.0478</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3500910878960899</v>
+        <v>0.3464750058430885</v>
       </c>
       <c r="J11" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K11" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0926798555908408</v>
+        <v>0.09232140506467035</v>
       </c>
       <c r="M11" t="n">
-        <v>6.13056024185048</v>
+        <v>6.098055488525307</v>
       </c>
       <c r="N11" t="n">
-        <v>56.41140003877445</v>
+        <v>56.00830260629878</v>
       </c>
       <c r="O11" t="n">
-        <v>7.510752295128261</v>
+        <v>7.48386949420544</v>
       </c>
       <c r="P11" t="n">
-        <v>355.8970050549995</v>
+        <v>355.9404793348269</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28531,28 +28743,28 @@
         <v>0.0536</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2426395431444107</v>
+        <v>0.236075762283466</v>
       </c>
       <c r="J12" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K12" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06086809604881083</v>
+        <v>0.05859276882767739</v>
       </c>
       <c r="M12" t="n">
-        <v>5.163072708249704</v>
+        <v>5.152144361627035</v>
       </c>
       <c r="N12" t="n">
-        <v>42.7060691994839</v>
+        <v>42.49278648900243</v>
       </c>
       <c r="O12" t="n">
-        <v>6.534988079521178</v>
+        <v>6.518649130686697</v>
       </c>
       <c r="P12" t="n">
-        <v>363.814875610718</v>
+        <v>363.8937857484308</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28609,28 +28821,28 @@
         <v>0.0468</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2360942994535022</v>
+        <v>0.2287191948735468</v>
       </c>
       <c r="J13" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K13" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06048456131979318</v>
+        <v>0.05770344590250198</v>
       </c>
       <c r="M13" t="n">
-        <v>5.250215220798575</v>
+        <v>5.238777128702521</v>
       </c>
       <c r="N13" t="n">
-        <v>40.70614272925919</v>
+        <v>40.53871537853398</v>
       </c>
       <c r="O13" t="n">
-        <v>6.380136576066314</v>
+        <v>6.367002071503824</v>
       </c>
       <c r="P13" t="n">
-        <v>372.1365563647989</v>
+        <v>372.225222887206</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28687,28 +28899,28 @@
         <v>0.0508</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1164422279339888</v>
+        <v>0.1044778576881559</v>
       </c>
       <c r="J14" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K14" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01912260186669323</v>
+        <v>0.01552985814875651</v>
       </c>
       <c r="M14" t="n">
-        <v>4.683638339658531</v>
+        <v>4.696672907161574</v>
       </c>
       <c r="N14" t="n">
-        <v>32.69778395935361</v>
+        <v>32.83692483485711</v>
       </c>
       <c r="O14" t="n">
-        <v>5.718197614576958</v>
+        <v>5.730351196467553</v>
       </c>
       <c r="P14" t="n">
-        <v>382.3000670522403</v>
+        <v>382.443905904177</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28765,28 +28977,28 @@
         <v>0.0555</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1068358226940875</v>
+        <v>0.09433621073728785</v>
       </c>
       <c r="J15" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K15" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01580986511641502</v>
+        <v>0.01242216698427667</v>
       </c>
       <c r="M15" t="n">
-        <v>4.704701001095144</v>
+        <v>4.720746759336195</v>
       </c>
       <c r="N15" t="n">
-        <v>33.4052097579566</v>
+        <v>33.57451337965121</v>
       </c>
       <c r="O15" t="n">
-        <v>5.779724020916276</v>
+        <v>5.794351851557791</v>
       </c>
       <c r="P15" t="n">
-        <v>376.9916847232896</v>
+        <v>377.141962444786</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28843,28 +29055,28 @@
         <v>0.0487</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.004352270014709162</v>
+        <v>-0.0168659289867489</v>
       </c>
       <c r="J16" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K16" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="L16" t="n">
-        <v>2.131333512545019e-05</v>
+        <v>0.0003221353420099771</v>
       </c>
       <c r="M16" t="n">
-        <v>5.336845186980011</v>
+        <v>5.343171776181195</v>
       </c>
       <c r="N16" t="n">
-        <v>41.82850823864623</v>
+        <v>41.93214624305251</v>
       </c>
       <c r="O16" t="n">
-        <v>6.467496288259177</v>
+        <v>6.47550355131186</v>
       </c>
       <c r="P16" t="n">
-        <v>377.6146686253992</v>
+        <v>377.7653749823107</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28921,28 +29133,28 @@
         <v>0.0534</v>
       </c>
       <c r="I17" t="n">
-        <v>0.03017726722683511</v>
+        <v>0.02065225282636065</v>
       </c>
       <c r="J17" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K17" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0009738066384197275</v>
+        <v>0.0004615428647857245</v>
       </c>
       <c r="M17" t="n">
-        <v>5.206764039016842</v>
+        <v>5.204694210305176</v>
       </c>
       <c r="N17" t="n">
-        <v>43.97089907364378</v>
+        <v>43.87601625038133</v>
       </c>
       <c r="O17" t="n">
-        <v>6.631055653034725</v>
+        <v>6.623897361099531</v>
       </c>
       <c r="P17" t="n">
-        <v>375.387591771167</v>
+        <v>375.5023058838162</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28999,28 +29211,28 @@
         <v>0.0579</v>
       </c>
       <c r="I18" t="n">
-        <v>0.04139712508212973</v>
+        <v>0.02949968036715307</v>
       </c>
       <c r="J18" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K18" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L18" t="n">
-        <v>0.00205519163816581</v>
+        <v>0.00105212385500475</v>
       </c>
       <c r="M18" t="n">
-        <v>5.14373594251397</v>
+        <v>5.146129585320323</v>
       </c>
       <c r="N18" t="n">
-        <v>39.1222771210065</v>
+        <v>39.20933550205708</v>
       </c>
       <c r="O18" t="n">
-        <v>6.254780341547295</v>
+        <v>6.261735821803494</v>
       </c>
       <c r="P18" t="n">
-        <v>376.1075360730568</v>
+        <v>376.2505675008703</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -29077,28 +29289,28 @@
         <v>0.053</v>
       </c>
       <c r="I19" t="n">
-        <v>0.09694195162897445</v>
+        <v>0.08950196271036598</v>
       </c>
       <c r="J19" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K19" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01017647953785616</v>
+        <v>0.008804688504166047</v>
       </c>
       <c r="M19" t="n">
-        <v>5.355412982077236</v>
+        <v>5.345119076591046</v>
       </c>
       <c r="N19" t="n">
-        <v>43.31011419898169</v>
+        <v>43.12801485817918</v>
       </c>
       <c r="O19" t="n">
-        <v>6.581042029875033</v>
+        <v>6.567192311648806</v>
       </c>
       <c r="P19" t="n">
-        <v>379.6306140880366</v>
+        <v>379.7196052292759</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -29155,28 +29367,28 @@
         <v>0.049</v>
       </c>
       <c r="I20" t="n">
-        <v>0.06736730269619014</v>
+        <v>0.05883483968480741</v>
       </c>
       <c r="J20" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K20" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="L20" t="n">
-        <v>0.005012433376680225</v>
+        <v>0.003875553132632548</v>
       </c>
       <c r="M20" t="n">
-        <v>5.087368525830215</v>
+        <v>5.082485634564724</v>
       </c>
       <c r="N20" t="n">
-        <v>41.68463039258245</v>
+        <v>41.55467976192132</v>
       </c>
       <c r="O20" t="n">
-        <v>6.45636355796221</v>
+        <v>6.446291938930576</v>
       </c>
       <c r="P20" t="n">
-        <v>384.8425699406878</v>
+        <v>384.946209334947</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -29233,28 +29445,28 @@
         <v>0.0506</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1974456354903442</v>
+        <v>0.1907042052811606</v>
       </c>
       <c r="J21" t="n">
+        <v>258</v>
+      </c>
+      <c r="K21" t="n">
         <v>256</v>
       </c>
-      <c r="K21" t="n">
-        <v>254</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.04286420250382417</v>
+        <v>0.04064943759883366</v>
       </c>
       <c r="M21" t="n">
-        <v>4.897118634613824</v>
+        <v>4.884446204779906</v>
       </c>
       <c r="N21" t="n">
-        <v>40.60426577348932</v>
+        <v>40.41073052177632</v>
       </c>
       <c r="O21" t="n">
-        <v>6.372147657853616</v>
+        <v>6.356943488955705</v>
       </c>
       <c r="P21" t="n">
-        <v>388.3116873753332</v>
+        <v>388.3931520518117</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -29311,28 +29523,28 @@
         <v>0.057</v>
       </c>
       <c r="I22" t="n">
-        <v>0.157381889805849</v>
+        <v>0.1545443712932117</v>
       </c>
       <c r="J22" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K22" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L22" t="n">
-        <v>0.03481238295686684</v>
+        <v>0.03414664815352164</v>
       </c>
       <c r="M22" t="n">
-        <v>4.372521528601094</v>
+        <v>4.34956620789952</v>
       </c>
       <c r="N22" t="n">
-        <v>32.53816871591853</v>
+        <v>32.30863446878391</v>
       </c>
       <c r="O22" t="n">
-        <v>5.704223761031691</v>
+        <v>5.684068478544563</v>
       </c>
       <c r="P22" t="n">
-        <v>387.2993715348159</v>
+        <v>387.3333095083483</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -29389,28 +29601,28 @@
         <v>0.0611</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1953201342640119</v>
+        <v>0.1942659824450322</v>
       </c>
       <c r="J23" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K23" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L23" t="n">
-        <v>0.05164415706668735</v>
+        <v>0.05194742555449305</v>
       </c>
       <c r="M23" t="n">
-        <v>4.386306275720955</v>
+        <v>4.356520022943969</v>
       </c>
       <c r="N23" t="n">
-        <v>33.19324909799992</v>
+        <v>32.93904601924724</v>
       </c>
       <c r="O23" t="n">
-        <v>5.761358268498838</v>
+        <v>5.739254831356353</v>
       </c>
       <c r="P23" t="n">
-        <v>385.2904437526173</v>
+        <v>385.3030520594453</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -29467,28 +29679,28 @@
         <v>0.064</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2585251310813488</v>
+        <v>0.2590791575882119</v>
       </c>
       <c r="J24" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K24" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L24" t="n">
-        <v>0.07380497911555306</v>
+        <v>0.0752753853282383</v>
       </c>
       <c r="M24" t="n">
-        <v>4.976141260966777</v>
+        <v>4.939745104058522</v>
       </c>
       <c r="N24" t="n">
-        <v>39.79287333871022</v>
+        <v>39.48435410574788</v>
       </c>
       <c r="O24" t="n">
-        <v>6.308159267069136</v>
+        <v>6.283657701191868</v>
       </c>
       <c r="P24" t="n">
-        <v>383.696317877742</v>
+        <v>383.6896862240434</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -29545,28 +29757,28 @@
         <v>0.0766</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2033095031169549</v>
+        <v>0.2042494160630079</v>
       </c>
       <c r="J25" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K25" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L25" t="n">
-        <v>0.06738503592008327</v>
+        <v>0.06905185508744993</v>
       </c>
       <c r="M25" t="n">
-        <v>4.128858681888544</v>
+        <v>4.101055839415037</v>
       </c>
       <c r="N25" t="n">
-        <v>27.10565329792385</v>
+        <v>26.89805606729854</v>
       </c>
       <c r="O25" t="n">
-        <v>5.206308989862573</v>
+        <v>5.18633358619541</v>
       </c>
       <c r="P25" t="n">
-        <v>377.592040603041</v>
+        <v>377.5807974204209</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -29623,28 +29835,28 @@
         <v>0.0496</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1490538743008962</v>
+        <v>0.1494174044501662</v>
       </c>
       <c r="J26" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K26" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L26" t="n">
-        <v>0.02787912633627021</v>
+        <v>0.02847919751436179</v>
       </c>
       <c r="M26" t="n">
-        <v>4.57741281900541</v>
+        <v>4.545388790379772</v>
       </c>
       <c r="N26" t="n">
-        <v>36.70567816157173</v>
+        <v>36.42301054009572</v>
       </c>
       <c r="O26" t="n">
-        <v>6.058521120007071</v>
+        <v>6.035147930257859</v>
       </c>
       <c r="P26" t="n">
-        <v>383.0153485113822</v>
+        <v>383.010996625415</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -29701,28 +29913,28 @@
         <v>0.0752</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1909361070269497</v>
+        <v>0.1929888744628311</v>
       </c>
       <c r="J27" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K27" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L27" t="n">
-        <v>0.06348068298651233</v>
+        <v>0.06577791767156915</v>
       </c>
       <c r="M27" t="n">
-        <v>3.86505012686645</v>
+        <v>3.845224505460902</v>
       </c>
       <c r="N27" t="n">
-        <v>25.48337129330296</v>
+        <v>25.29785279176729</v>
       </c>
       <c r="O27" t="n">
-        <v>5.048105713364465</v>
+        <v>5.029697087476272</v>
       </c>
       <c r="P27" t="n">
-        <v>366.915467789576</v>
+        <v>366.8909127401085</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -29779,28 +29991,28 @@
         <v>0.0784</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1811689281465899</v>
+        <v>0.1871710215420941</v>
       </c>
       <c r="J28" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K28" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L28" t="n">
-        <v>0.04289913740717266</v>
+        <v>0.04627144216550949</v>
       </c>
       <c r="M28" t="n">
-        <v>4.587960182896007</v>
+        <v>4.577334695221871</v>
       </c>
       <c r="N28" t="n">
-        <v>34.64806780079201</v>
+        <v>34.48383036487046</v>
       </c>
       <c r="O28" t="n">
-        <v>5.886260935499887</v>
+        <v>5.872293450166678</v>
       </c>
       <c r="P28" t="n">
-        <v>363.3269250111661</v>
+        <v>363.2549845811708</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -29857,28 +30069,28 @@
         <v>0.1741</v>
       </c>
       <c r="I29" t="n">
-        <v>0.02939015657388858</v>
+        <v>0.03671544668836917</v>
       </c>
       <c r="J29" t="n">
+        <v>258</v>
+      </c>
+      <c r="K29" t="n">
         <v>256</v>
       </c>
-      <c r="K29" t="n">
-        <v>254</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.001550610635224214</v>
+        <v>0.002445339789513334</v>
       </c>
       <c r="M29" t="n">
-        <v>3.906196246777758</v>
+        <v>3.904610575902472</v>
       </c>
       <c r="N29" t="n">
-        <v>26.38554095744536</v>
+        <v>26.32884209151612</v>
       </c>
       <c r="O29" t="n">
-        <v>5.136685795086688</v>
+        <v>5.131163814527472</v>
       </c>
       <c r="P29" t="n">
-        <v>371.6851860168828</v>
+        <v>371.5974211564361</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -29916,7 +30128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD257"/>
+  <dimension ref="A1:AD259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68579,6 +68791,310 @@
         </is>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>-35.6320032223985,174.5151443344246</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>-35.63277753760321,174.51504338398652</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>-35.63333602502926,174.5144072449978</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>-35.63395269334537,174.51387696235324</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>-35.63448173820905,174.51323315591713</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>-35.63496784305478,174.51255391457926</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>-35.63546975481137,174.5118993350698</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>-35.63599989496336,174.51128143758987</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>-35.636543278331196,174.5106810332859</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>-35.6370972711605,174.5100951303097</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>-35.63764801902002,174.50950494983098</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>-35.638227142518495,174.5089571873659</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>-35.63878852935244,174.50842289431853</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>-35.639395206888494,174.5079516214138</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>-35.64002628344551,174.50749844033044</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>-35.64067248863235,174.50707797511714</t>
+        </is>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>-35.64130246811749,174.5066201530531</t>
+        </is>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>-35.64196609138993,174.5062342650732</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>-35.64260605138027,174.50580107312007</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>-35.64325927053772,174.50541986120348</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>-35.643901432787956,174.5050292886652</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>-35.64456103014767,174.50465254096238</t>
+        </is>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>-35.64521312381639,174.50428721972415</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>-35.64586829141168,174.50392468585454</t>
+        </is>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>-35.64656932389423,174.50367807267432</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>-35.64722504696422,174.50325227787684</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>-35.647908011653456,174.5029497442613</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>-35.64862539671607,174.5028391475905</t>
+        </is>
+      </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>-35.63200154564357,174.51514017649893</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>-35.63277761744858,174.51504358198497</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>-35.63335470902043,174.5144535768643</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>-35.63395264502057,174.51387686914055</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>-35.63448226892227,174.5132339075792</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>-35.63497252337164,174.5125600429948</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>-35.63546926214409,174.51189868997193</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>-35.63600056960422,174.51128232777535</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>-35.636543705305705,174.51068160242187</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>-35.637097149330074,174.51009496751578</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>-35.637651795778616,174.5095099964611</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>-35.6382276171359,174.50895785248295</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>-35.638791233827924,174.50842785235028</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>-35.63939348668319,174.50794761417103</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>-35.640027668008635,174.50750166569316</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>-35.64067248863235,174.50707797511714</t>
+        </is>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>-35.64130786352143,174.5066316386722</t>
+        </is>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>-35.641965128444234,174.50623226846727</t>
+        </is>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>-35.642609765615354,174.5058087743655</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>-35.64326067537272,174.50542307351608</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>-35.6439030784959,174.50503358808822</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>-35.64456144079018,174.50465364668258</t>
+        </is>
+      </c>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>-35.645214441187846,174.50429133178088</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>-35.64586884935023,174.50392678616174</t>
+        </is>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>-35.64657175810664,174.50368743829748</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>-35.647226223056144,174.50325680287378</t>
+        </is>
+      </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>-35.64791175734292,174.50296783561353</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>-35.64862522802048,174.50283806269547</t>
+        </is>
+      </c>
+      <c r="AD259" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0094/nzd0094.xlsx
+++ b/data/nzd0094/nzd0094.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD259"/>
+  <dimension ref="A1:AD260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25149,6 +25149,102 @@
         </is>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>387.43</v>
+      </c>
+      <c r="C260" t="n">
+        <v>419.61</v>
+      </c>
+      <c r="D260" t="n">
+        <v>395.15</v>
+      </c>
+      <c r="E260" t="n">
+        <v>379.62</v>
+      </c>
+      <c r="F260" t="n">
+        <v>370.01</v>
+      </c>
+      <c r="G260" t="n">
+        <v>364.15</v>
+      </c>
+      <c r="H260" t="n">
+        <v>357.38</v>
+      </c>
+      <c r="I260" t="n">
+        <v>358.52</v>
+      </c>
+      <c r="J260" t="n">
+        <v>360.24</v>
+      </c>
+      <c r="K260" t="n">
+        <v>364.29</v>
+      </c>
+      <c r="L260" t="n">
+        <v>368.69</v>
+      </c>
+      <c r="M260" t="n">
+        <v>375.42</v>
+      </c>
+      <c r="N260" t="n">
+        <v>380.47</v>
+      </c>
+      <c r="O260" t="n">
+        <v>372.77</v>
+      </c>
+      <c r="P260" t="n">
+        <v>369.56</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>368.87</v>
+      </c>
+      <c r="R260" t="n">
+        <v>374.54</v>
+      </c>
+      <c r="S260" t="n">
+        <v>375.66</v>
+      </c>
+      <c r="T260" t="n">
+        <v>380.7</v>
+      </c>
+      <c r="U260" t="n">
+        <v>388.67</v>
+      </c>
+      <c r="V260" t="n">
+        <v>389.15</v>
+      </c>
+      <c r="W260" t="n">
+        <v>388.71</v>
+      </c>
+      <c r="X260" t="n">
+        <v>390.59</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>384.74</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>392.94</v>
+      </c>
+      <c r="AA260" t="n">
+        <v>375</v>
+      </c>
+      <c r="AB260" t="n">
+        <v>375.48</v>
+      </c>
+      <c r="AC260" t="n">
+        <v>380.17</v>
+      </c>
+      <c r="AD260" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25160,7 +25256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B262"/>
+  <dimension ref="A1:B263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27783,6 +27879,16 @@
       </c>
       <c r="B262" t="n">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>-0.43</v>
       </c>
     </row>
   </sheetData>
@@ -27951,28 +28057,28 @@
         <v>0.0102</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9035317750002421</v>
+        <v>0.8973939765620073</v>
       </c>
       <c r="J2" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K2" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03263468359010058</v>
+        <v>0.03247339969632301</v>
       </c>
       <c r="M2" t="n">
-        <v>26.29625004604875</v>
+        <v>26.209975518894</v>
       </c>
       <c r="N2" t="n">
-        <v>1083.356797584514</v>
+        <v>1079.018000732514</v>
       </c>
       <c r="O2" t="n">
-        <v>32.91438587585243</v>
+        <v>32.84840940947542</v>
       </c>
       <c r="P2" t="n">
-        <v>369.9430680425734</v>
+        <v>370.0206726933344</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -28033,28 +28139,28 @@
         <v>0.0104</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8973721608038394</v>
+        <v>0.9079539378270287</v>
       </c>
       <c r="J3" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K3" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04933317564817508</v>
+        <v>0.05080989463444707</v>
       </c>
       <c r="M3" t="n">
-        <v>21.72566601057404</v>
+        <v>21.69474043184305</v>
       </c>
       <c r="N3" t="n">
-        <v>740.2829872461078</v>
+        <v>737.7096974323757</v>
       </c>
       <c r="O3" t="n">
-        <v>27.2081419293216</v>
+        <v>27.16081179626956</v>
       </c>
       <c r="P3" t="n">
-        <v>383.2798996419119</v>
+        <v>383.1493788141672</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -28115,28 +28221,28 @@
         <v>0.0106</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3606883653838632</v>
+        <v>0.3643539443695112</v>
       </c>
       <c r="J4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K4" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00885299222349567</v>
+        <v>0.009109585757375083</v>
       </c>
       <c r="M4" t="n">
-        <v>20.80922394905328</v>
+        <v>20.74461954996387</v>
       </c>
       <c r="N4" t="n">
-        <v>661.4117666346567</v>
+        <v>658.7373532440118</v>
       </c>
       <c r="O4" t="n">
-        <v>25.71792695056615</v>
+        <v>25.66587916366809</v>
       </c>
       <c r="P4" t="n">
-        <v>381.3000646898298</v>
+        <v>381.2541951930827</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -28197,28 +28303,28 @@
         <v>0.0239</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8256743349068584</v>
+        <v>0.8287752900894653</v>
       </c>
       <c r="J5" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K5" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08848283745521768</v>
+        <v>0.08976664747263741</v>
       </c>
       <c r="M5" t="n">
-        <v>14.89686823595663</v>
+        <v>14.85225413971714</v>
       </c>
       <c r="N5" t="n">
-        <v>335.8829533583887</v>
+        <v>334.6200195515981</v>
       </c>
       <c r="O5" t="n">
-        <v>18.32710979282846</v>
+        <v>18.29262199772351</v>
       </c>
       <c r="P5" t="n">
-        <v>353.628291394464</v>
+        <v>353.5909041766645</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28275,28 +28381,28 @@
         <v>0.0308</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3741257605766752</v>
+        <v>0.3781844897022197</v>
       </c>
       <c r="J6" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K6" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03182514780980494</v>
+        <v>0.03275300286935745</v>
       </c>
       <c r="M6" t="n">
-        <v>11.61608501780749</v>
+        <v>11.58886554925779</v>
       </c>
       <c r="N6" t="n">
-        <v>198.8792537056043</v>
+        <v>198.1921963199647</v>
       </c>
       <c r="O6" t="n">
-        <v>14.10245559133601</v>
+        <v>14.07807502181902</v>
       </c>
       <c r="P6" t="n">
-        <v>355.104553627757</v>
+        <v>355.0550693663151</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28353,28 +28459,28 @@
         <v>0.0359</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2876798095174832</v>
+        <v>0.2907179484918286</v>
       </c>
       <c r="J7" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K7" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02598033111056319</v>
+        <v>0.02672977147908839</v>
       </c>
       <c r="M7" t="n">
-        <v>10.12157755442545</v>
+        <v>10.0929416960366</v>
       </c>
       <c r="N7" t="n">
-        <v>146.0814861976805</v>
+        <v>145.5639431312231</v>
       </c>
       <c r="O7" t="n">
-        <v>12.08641742608952</v>
+        <v>12.06498831873546</v>
       </c>
       <c r="P7" t="n">
-        <v>352.7640580568375</v>
+        <v>352.7272069350196</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28431,28 +28537,28 @@
         <v>0.0369</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1931126630028509</v>
+        <v>0.1924408213361355</v>
       </c>
       <c r="J8" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K8" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01674927645631052</v>
+        <v>0.01677485772965337</v>
       </c>
       <c r="M8" t="n">
-        <v>8.209532810082091</v>
+        <v>8.181074549180414</v>
       </c>
       <c r="N8" t="n">
-        <v>103.0725683143961</v>
+        <v>102.6739952082329</v>
       </c>
       <c r="O8" t="n">
-        <v>10.15246611983493</v>
+        <v>10.13281773290297</v>
       </c>
       <c r="P8" t="n">
-        <v>352.9794982985472</v>
+        <v>352.9876474053891</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28509,28 +28615,28 @@
         <v>0.0422</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2316199649906431</v>
+        <v>0.231337101134567</v>
       </c>
       <c r="J9" t="n">
+        <v>259</v>
+      </c>
+      <c r="K9" t="n">
         <v>258</v>
       </c>
-      <c r="K9" t="n">
-        <v>257</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.03575565816560022</v>
+        <v>0.03596564919946066</v>
       </c>
       <c r="M9" t="n">
-        <v>6.667449551458214</v>
+        <v>6.642995240225289</v>
       </c>
       <c r="N9" t="n">
-        <v>68.65516367792218</v>
+        <v>68.38950399772783</v>
       </c>
       <c r="O9" t="n">
-        <v>8.285841156932841</v>
+        <v>8.269794676878492</v>
       </c>
       <c r="P9" t="n">
-        <v>352.617480185073</v>
+        <v>352.620893648624</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28587,28 +28693,28 @@
         <v>0.045</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2938860118853702</v>
+        <v>0.2927566294608241</v>
       </c>
       <c r="J10" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K10" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06108053741700548</v>
+        <v>0.06112044764024827</v>
       </c>
       <c r="M10" t="n">
-        <v>6.425476020723381</v>
+        <v>6.40551408218398</v>
       </c>
       <c r="N10" t="n">
-        <v>63.07947877898627</v>
+        <v>62.84115734599537</v>
       </c>
       <c r="O10" t="n">
-        <v>7.942259047587548</v>
+        <v>7.927241471407022</v>
       </c>
       <c r="P10" t="n">
-        <v>353.6853456687534</v>
+        <v>353.6989819112567</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28665,28 +28771,28 @@
         <v>0.0478</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3464750058430885</v>
+        <v>0.3456555213262288</v>
       </c>
       <c r="J11" t="n">
+        <v>259</v>
+      </c>
+      <c r="K11" t="n">
         <v>258</v>
       </c>
-      <c r="K11" t="n">
-        <v>257</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.09232140506467035</v>
+        <v>0.09263369237493413</v>
       </c>
       <c r="M11" t="n">
-        <v>6.098055488525307</v>
+        <v>6.077820044093136</v>
       </c>
       <c r="N11" t="n">
-        <v>56.00830260629878</v>
+        <v>55.79495620869923</v>
       </c>
       <c r="O11" t="n">
-        <v>7.48386949420544</v>
+        <v>7.469602145275157</v>
       </c>
       <c r="P11" t="n">
-        <v>355.9404793348269</v>
+        <v>355.9503684757292</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28743,28 +28849,28 @@
         <v>0.0536</v>
       </c>
       <c r="I12" t="n">
-        <v>0.236075762283466</v>
+        <v>0.234779263974034</v>
       </c>
       <c r="J12" t="n">
+        <v>259</v>
+      </c>
+      <c r="K12" t="n">
         <v>258</v>
       </c>
-      <c r="K12" t="n">
-        <v>257</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.05859276882767739</v>
+        <v>0.05844340445511331</v>
       </c>
       <c r="M12" t="n">
-        <v>5.152144361627035</v>
+        <v>5.137874008676148</v>
       </c>
       <c r="N12" t="n">
-        <v>42.49278648900243</v>
+        <v>42.33744713636125</v>
       </c>
       <c r="O12" t="n">
-        <v>6.518649130686697</v>
+        <v>6.506723225738225</v>
       </c>
       <c r="P12" t="n">
-        <v>363.8937857484308</v>
+        <v>363.909431259966</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28821,28 +28927,28 @@
         <v>0.0468</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2287191948735468</v>
+        <v>0.2262592872869581</v>
       </c>
       <c r="J13" t="n">
+        <v>259</v>
+      </c>
+      <c r="K13" t="n">
         <v>258</v>
       </c>
-      <c r="K13" t="n">
-        <v>257</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.05770344590250198</v>
+        <v>0.05695029731933765</v>
       </c>
       <c r="M13" t="n">
-        <v>5.238777128702521</v>
+        <v>5.228140642088213</v>
       </c>
       <c r="N13" t="n">
-        <v>40.53871537853398</v>
+        <v>40.4152888224765</v>
       </c>
       <c r="O13" t="n">
-        <v>6.367002071503824</v>
+        <v>6.357302008122352</v>
       </c>
       <c r="P13" t="n">
-        <v>372.225222887206</v>
+        <v>372.2549078565127</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28899,28 +29005,28 @@
         <v>0.0508</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1044778576881559</v>
+        <v>0.1005066845518569</v>
       </c>
       <c r="J14" t="n">
+        <v>259</v>
+      </c>
+      <c r="K14" t="n">
         <v>258</v>
       </c>
-      <c r="K14" t="n">
-        <v>257</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.01552985814875651</v>
+        <v>0.0144714788030309</v>
       </c>
       <c r="M14" t="n">
-        <v>4.696672907161574</v>
+        <v>4.694658029172278</v>
       </c>
       <c r="N14" t="n">
-        <v>32.83692483485711</v>
+        <v>32.7974779648266</v>
       </c>
       <c r="O14" t="n">
-        <v>5.730351196467553</v>
+        <v>5.726908237856321</v>
       </c>
       <c r="P14" t="n">
-        <v>382.443905904177</v>
+        <v>382.4918280917036</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28977,28 +29083,28 @@
         <v>0.0555</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09433621073728785</v>
+        <v>0.08860855350854809</v>
       </c>
       <c r="J15" t="n">
+        <v>259</v>
+      </c>
+      <c r="K15" t="n">
         <v>258</v>
       </c>
-      <c r="K15" t="n">
-        <v>257</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.01242216698427667</v>
+        <v>0.01100902056669428</v>
       </c>
       <c r="M15" t="n">
-        <v>4.720746759336195</v>
+        <v>4.726298241263861</v>
       </c>
       <c r="N15" t="n">
-        <v>33.57451337965121</v>
+        <v>33.62708423517793</v>
       </c>
       <c r="O15" t="n">
-        <v>5.794351851557791</v>
+        <v>5.798886465104997</v>
       </c>
       <c r="P15" t="n">
-        <v>377.141962444786</v>
+        <v>377.2110810287365</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29055,28 +29161,28 @@
         <v>0.0487</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0168659289867489</v>
+        <v>-0.02330238870278984</v>
       </c>
       <c r="J16" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K16" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0003221353420099771</v>
+        <v>0.0006165703448709481</v>
       </c>
       <c r="M16" t="n">
-        <v>5.343171776181195</v>
+        <v>5.346716147982701</v>
       </c>
       <c r="N16" t="n">
-        <v>41.93214624305251</v>
+        <v>41.99987635776308</v>
       </c>
       <c r="O16" t="n">
-        <v>6.47550355131186</v>
+        <v>6.480731159195162</v>
       </c>
       <c r="P16" t="n">
-        <v>377.7653749823107</v>
+        <v>377.8431852836818</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29133,28 +29239,28 @@
         <v>0.0534</v>
       </c>
       <c r="I17" t="n">
-        <v>0.02065225282636065</v>
+        <v>0.01468062387709896</v>
       </c>
       <c r="J17" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K17" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0004615428647857245</v>
+        <v>0.0002341971593903258</v>
       </c>
       <c r="M17" t="n">
-        <v>5.204694210305176</v>
+        <v>5.208407319547976</v>
       </c>
       <c r="N17" t="n">
-        <v>43.87601625038133</v>
+        <v>43.90391955793551</v>
       </c>
       <c r="O17" t="n">
-        <v>6.623897361099531</v>
+        <v>6.626003286894409</v>
       </c>
       <c r="P17" t="n">
-        <v>375.5023058838162</v>
+        <v>375.5744968503907</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29211,28 +29317,28 @@
         <v>0.0579</v>
       </c>
       <c r="I18" t="n">
-        <v>0.02949968036715307</v>
+        <v>0.02742257634124906</v>
       </c>
       <c r="J18" t="n">
+        <v>259</v>
+      </c>
+      <c r="K18" t="n">
         <v>258</v>
       </c>
-      <c r="K18" t="n">
-        <v>257</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.00105212385500475</v>
+        <v>0.0009165213059417754</v>
       </c>
       <c r="M18" t="n">
-        <v>5.146129585320323</v>
+        <v>5.133478210664279</v>
       </c>
       <c r="N18" t="n">
-        <v>39.20933550205708</v>
+        <v>39.0813890225861</v>
       </c>
       <c r="O18" t="n">
-        <v>6.261735821803494</v>
+        <v>6.251510939171913</v>
       </c>
       <c r="P18" t="n">
-        <v>376.2505675008703</v>
+        <v>376.2756329828388</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -29289,28 +29395,28 @@
         <v>0.053</v>
       </c>
       <c r="I19" t="n">
-        <v>0.08950196271036598</v>
+        <v>0.08417360265059998</v>
       </c>
       <c r="J19" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K19" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L19" t="n">
-        <v>0.008804688504166047</v>
+        <v>0.007832616155726724</v>
       </c>
       <c r="M19" t="n">
-        <v>5.345119076591046</v>
+        <v>5.346529686664934</v>
       </c>
       <c r="N19" t="n">
-        <v>43.12801485817918</v>
+        <v>43.12125858656425</v>
       </c>
       <c r="O19" t="n">
-        <v>6.567192311648806</v>
+        <v>6.566677895752482</v>
       </c>
       <c r="P19" t="n">
-        <v>379.7196052292759</v>
+        <v>379.7835779080973</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -29367,28 +29473,28 @@
         <v>0.049</v>
       </c>
       <c r="I20" t="n">
-        <v>0.05883483968480741</v>
+        <v>0.05393115134957422</v>
       </c>
       <c r="J20" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K20" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L20" t="n">
-        <v>0.003875553132632548</v>
+        <v>0.003276073154664938</v>
       </c>
       <c r="M20" t="n">
-        <v>5.082485634564724</v>
+        <v>5.08314092851581</v>
       </c>
       <c r="N20" t="n">
-        <v>41.55467976192132</v>
+        <v>41.52345990683848</v>
       </c>
       <c r="O20" t="n">
-        <v>6.446291938930576</v>
+        <v>6.443869948007833</v>
       </c>
       <c r="P20" t="n">
-        <v>384.946209334947</v>
+        <v>385.0059953881928</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -29445,28 +29551,28 @@
         <v>0.0506</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1907042052811606</v>
+        <v>0.1866437342849086</v>
       </c>
       <c r="J21" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K21" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L21" t="n">
-        <v>0.04064943759883366</v>
+        <v>0.03924016814003239</v>
       </c>
       <c r="M21" t="n">
-        <v>4.884446204779906</v>
+        <v>4.880694482892195</v>
       </c>
       <c r="N21" t="n">
-        <v>40.41073052177632</v>
+        <v>40.34435121195274</v>
       </c>
       <c r="O21" t="n">
-        <v>6.356943488955705</v>
+        <v>6.351720334834709</v>
       </c>
       <c r="P21" t="n">
-        <v>388.3931520518117</v>
+        <v>388.44240355498</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -29523,28 +29629,28 @@
         <v>0.057</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1545443712932117</v>
+        <v>0.1526096643275228</v>
       </c>
       <c r="J22" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K22" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L22" t="n">
-        <v>0.03414664815352164</v>
+        <v>0.03357911163011729</v>
       </c>
       <c r="M22" t="n">
-        <v>4.34956620789952</v>
+        <v>4.34012876691485</v>
       </c>
       <c r="N22" t="n">
-        <v>32.30863446878391</v>
+        <v>32.20495342701347</v>
       </c>
       <c r="O22" t="n">
-        <v>5.684068478544563</v>
+        <v>5.674940830265411</v>
       </c>
       <c r="P22" t="n">
-        <v>387.3333095083483</v>
+        <v>387.3565377410393</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -29601,28 +29707,28 @@
         <v>0.0611</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1942659824450322</v>
+        <v>0.1927622144891665</v>
       </c>
       <c r="J23" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K23" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L23" t="n">
-        <v>0.05194742555449305</v>
+        <v>0.05158285289571629</v>
       </c>
       <c r="M23" t="n">
-        <v>4.356520022943969</v>
+        <v>4.345632578214183</v>
       </c>
       <c r="N23" t="n">
-        <v>32.93904601924724</v>
+        <v>32.82459288199113</v>
       </c>
       <c r="O23" t="n">
-        <v>5.739254831356353</v>
+        <v>5.729275074735994</v>
       </c>
       <c r="P23" t="n">
-        <v>385.3030520594453</v>
+        <v>385.3211064070089</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -29679,28 +29785,28 @@
         <v>0.064</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2590791575882119</v>
+        <v>0.2590110205641126</v>
       </c>
       <c r="J24" t="n">
+        <v>259</v>
+      </c>
+      <c r="K24" t="n">
         <v>258</v>
       </c>
-      <c r="K24" t="n">
-        <v>257</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.0752753853282383</v>
+        <v>0.07583142878077209</v>
       </c>
       <c r="M24" t="n">
-        <v>4.939745104058522</v>
+        <v>4.920950074890305</v>
       </c>
       <c r="N24" t="n">
-        <v>39.48435410574788</v>
+        <v>39.33134017493033</v>
       </c>
       <c r="O24" t="n">
-        <v>6.283657701191868</v>
+        <v>6.271470335968298</v>
       </c>
       <c r="P24" t="n">
-        <v>383.6896862240434</v>
+        <v>383.6905046997456</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -29757,28 +29863,28 @@
         <v>0.0766</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2042494160630079</v>
+        <v>0.205613206440765</v>
       </c>
       <c r="J25" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K25" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L25" t="n">
-        <v>0.06905185508744993</v>
+        <v>0.07044168042358467</v>
       </c>
       <c r="M25" t="n">
-        <v>4.101055839415037</v>
+        <v>4.091234517754263</v>
       </c>
       <c r="N25" t="n">
-        <v>26.89805606729854</v>
+        <v>26.80466853501193</v>
       </c>
       <c r="O25" t="n">
-        <v>5.18633358619541</v>
+        <v>5.177322525689503</v>
       </c>
       <c r="P25" t="n">
-        <v>377.5807974204209</v>
+        <v>377.5644236538516</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -29835,28 +29941,28 @@
         <v>0.0496</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1494174044501662</v>
+        <v>0.1542762816987199</v>
       </c>
       <c r="J26" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K26" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L26" t="n">
-        <v>0.02847919751436179</v>
+        <v>0.03044725953083738</v>
       </c>
       <c r="M26" t="n">
-        <v>4.545388790379772</v>
+        <v>4.550935787571116</v>
       </c>
       <c r="N26" t="n">
-        <v>36.42301054009572</v>
+        <v>36.41522943468278</v>
       </c>
       <c r="O26" t="n">
-        <v>6.035147930257859</v>
+        <v>6.034503246720709</v>
       </c>
       <c r="P26" t="n">
-        <v>383.010996625415</v>
+        <v>382.9526605914069</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -29913,28 +30019,28 @@
         <v>0.0752</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1929888744628311</v>
+        <v>0.195386730421503</v>
       </c>
       <c r="J27" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K27" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L27" t="n">
-        <v>0.06577791767156915</v>
+        <v>0.06776656481698595</v>
       </c>
       <c r="M27" t="n">
-        <v>3.845224505460902</v>
+        <v>3.842236876640764</v>
       </c>
       <c r="N27" t="n">
-        <v>25.29785279176729</v>
+        <v>25.23253185420323</v>
       </c>
       <c r="O27" t="n">
-        <v>5.029697087476272</v>
+        <v>5.023199364369607</v>
       </c>
       <c r="P27" t="n">
-        <v>366.8909127401085</v>
+        <v>366.8621239068871</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -29991,28 +30097,28 @@
         <v>0.0784</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1871710215420941</v>
+        <v>0.193099589947488</v>
       </c>
       <c r="J28" t="n">
+        <v>259</v>
+      </c>
+      <c r="K28" t="n">
         <v>258</v>
       </c>
-      <c r="K28" t="n">
-        <v>257</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.04627144216550949</v>
+        <v>0.04923183206624937</v>
       </c>
       <c r="M28" t="n">
-        <v>4.577334695221871</v>
+        <v>4.584504311884517</v>
       </c>
       <c r="N28" t="n">
-        <v>34.48383036487046</v>
+        <v>34.54782639918924</v>
       </c>
       <c r="O28" t="n">
-        <v>5.872293450166678</v>
+        <v>5.877739905711143</v>
       </c>
       <c r="P28" t="n">
-        <v>363.2549845811708</v>
+        <v>363.1836643777976</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -30069,28 +30175,28 @@
         <v>0.1741</v>
       </c>
       <c r="I29" t="n">
-        <v>0.03671544668836917</v>
+        <v>0.04297117465586272</v>
       </c>
       <c r="J29" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K29" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L29" t="n">
-        <v>0.002445339789513334</v>
+        <v>0.003346892533843238</v>
       </c>
       <c r="M29" t="n">
-        <v>3.904610575902472</v>
+        <v>3.914533816464715</v>
       </c>
       <c r="N29" t="n">
-        <v>26.32884209151612</v>
+        <v>26.44741147080918</v>
       </c>
       <c r="O29" t="n">
-        <v>5.131163814527472</v>
+        <v>5.142704684386337</v>
       </c>
       <c r="P29" t="n">
-        <v>371.5974211564361</v>
+        <v>371.5221860079334</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -30128,7 +30234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD259"/>
+  <dimension ref="A1:AD260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69095,6 +69201,158 @@
         </is>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>-35.632029012467804,174.5152082873031</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>-35.632808637344766,174.51512050441013</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>-35.6333621347041,174.51447199081707</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>-35.63396622428827,174.5139030619128</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>-35.63448969890682,174.5132444308489</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>-35.63498366991438,174.51257463830316</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>-35.63546975481137,174.5118993350698</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>-35.63600461744923,174.51128766888843</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>-35.636546816119825,174.5106857489842</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>-35.63710433732495,174.51010457235745</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>-35.63766397886937,174.50952627591633</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>-35.63823556697683,174.5089689931952</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>-35.63880110015341,174.50844593998744</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>-35.63939612992542,174.5079537716417</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>-35.640025192577525,174.50749589913565</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>-35.640665563495,174.50706235051354</t>
+        </is>
+      </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>-35.64132530865309,174.50666877551762</t>
+        </is>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>-35.6419561409494,174.50621363348094</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>-35.64260380449707,174.50579641434229</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>-35.64325607773061,174.50541256049348</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>-35.64389974880757,174.50502488925576</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>-35.64455681172849,174.50464118220103</t>
+        </is>
+      </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>-35.645212530999196,174.50428536929869</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>-35.64587169483619,174.5039374977289</t>
+        </is>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>-35.646586144560246,174.50374279019366</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>-35.647230325701,174.5032725877479</t>
+        </is>
+      </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>-35.64791800754051,174.50299802355394</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>-35.64863082870881,174.50287408121335</t>
+        </is>
+      </c>
+      <c r="AD260" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
